--- a/outputs/task_schedule_detail.xlsx
+++ b/outputs/task_schedule_detail.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,193 +478,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>477.3</v>
+        <v>476.5</v>
       </c>
       <c r="D2" t="n">
-        <v>478.8</v>
+        <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>8.161421775123378</v>
+        <v>33.38109111249314</v>
       </c>
       <c r="F2" t="n">
-        <v>1.865053761592514</v>
+        <v>1.06618071060595</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03894584876119576</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>0.3711620426859015</v>
+      </c>
+      <c r="H2" t="n">
+        <v>344.4532502497294</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>477.3</v>
+        <v>477.4</v>
       </c>
       <c r="D3" t="n">
-        <v>478.8</v>
+        <v>477.9</v>
       </c>
       <c r="E3" t="n">
-        <v>18.51165536324877</v>
+        <v>17.87435385414754</v>
       </c>
       <c r="F3" t="n">
-        <v>1.865053761592514</v>
+        <v>1.427645528198585</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03894584876119576</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>0.5013294664455339</v>
+      </c>
+      <c r="H3" t="n">
+        <v>74.03283900677513</v>
+      </c>
       <c r="I3" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>477.3</v>
+        <v>481.7</v>
       </c>
       <c r="D4" t="n">
-        <v>478.8</v>
+        <v>482.2</v>
       </c>
       <c r="E4" t="n">
-        <v>23.95545290583382</v>
+        <v>20.6519103635131</v>
       </c>
       <c r="F4" t="n">
-        <v>1.865053761592514</v>
+        <v>1.410381720137351</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03894584876119576</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>0.5320129691831204</v>
+      </c>
+      <c r="H4" t="n">
+        <v>133.0221469261027</v>
+      </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>477.5</v>
+        <v>488.6</v>
       </c>
       <c r="D5" t="n">
-        <v>479</v>
+        <v>489.1</v>
       </c>
       <c r="E5" t="n">
-        <v>15.71915157067668</v>
+        <v>14.68507732381272</v>
       </c>
       <c r="F5" t="n">
-        <v>1.858594428028922</v>
+        <v>1.476364233782371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9570591196432338</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>1.345799168991392</v>
+      </c>
+      <c r="H5" t="n">
+        <v>69.256672542974</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>477.5</v>
+        <v>494.6</v>
       </c>
       <c r="D6" t="n">
-        <v>479</v>
+        <v>495.1</v>
       </c>
       <c r="E6" t="n">
-        <v>7.463485666996357</v>
+        <v>32.60564880278061</v>
       </c>
       <c r="F6" t="n">
-        <v>1.858594428028922</v>
+        <v>1.479338843909856</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9570591196432338</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>0.8107513963713128</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.24683203751152</v>
+      </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>477.5</v>
+        <v>507.8</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>508.3</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54689737828631</v>
+        <v>28.02360910634154</v>
       </c>
       <c r="F7" t="n">
-        <v>1.858594428028922</v>
+        <v>0.7000998390268554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9570591196432338</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>0.3671570183100276</v>
+      </c>
+      <c r="H7" t="n">
+        <v>299.5945123027456</v>
+      </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,19 +685,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>508.4</v>
+        <v>513.8</v>
       </c>
       <c r="D8" t="n">
-        <v>509.9</v>
+        <v>515.3</v>
       </c>
       <c r="E8" t="n">
-        <v>16.86413639470659</v>
+        <v>9.762320856936592</v>
       </c>
       <c r="F8" t="n">
-        <v>1.368627202665584</v>
+        <v>1.11416978120803</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3549381677681985</v>
+        <v>0.2244982764903906</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
@@ -695,7 +707,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,22 +716,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>508.7</v>
+        <v>750.3</v>
       </c>
       <c r="D9" t="n">
-        <v>509.2</v>
+        <v>750.8</v>
       </c>
       <c r="E9" t="n">
-        <v>33.11613377032513</v>
+        <v>22.3801720124686</v>
       </c>
       <c r="F9" t="n">
-        <v>1.413602857059988</v>
+        <v>1.380934839132107</v>
       </c>
       <c r="G9" t="n">
-        <v>1.160139368790909</v>
+        <v>0.13836779743862</v>
       </c>
       <c r="H9" t="n">
-        <v>279.8709426975848</v>
+        <v>269.2708992618764</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -728,40 +740,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>模拟射击</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>508.7</v>
+        <v>751</v>
       </c>
       <c r="D10" t="n">
-        <v>509.2</v>
+        <v>752.5</v>
       </c>
       <c r="E10" t="n">
-        <v>28.98587359315943</v>
+        <v>13.63045935957495</v>
       </c>
       <c r="F10" t="n">
-        <v>1.413602857059988</v>
+        <v>1.908200684706482</v>
       </c>
       <c r="G10" t="n">
-        <v>1.160139368790909</v>
-      </c>
-      <c r="H10" t="n">
-        <v>299.5085276481853</v>
-      </c>
+        <v>0.2039413398541113</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -770,53 +780,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>509</v>
+        <v>762</v>
       </c>
       <c r="D11" t="n">
-        <v>510.5</v>
+        <v>763.5</v>
       </c>
       <c r="E11" t="n">
-        <v>9.456402839060875</v>
+        <v>29.76263534772398</v>
       </c>
       <c r="F11" t="n">
-        <v>1.035871434042922</v>
+        <v>1.000391786158068</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9719349496075563</v>
+        <v>0.2666408679073409</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>模拟射击</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>764.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>766.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>21.72832706699923</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.523432666310211</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.4568397284056099</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
         <v>0.85</v>
       </c>
     </row>

--- a/outputs/task_schedule_detail.xlsx
+++ b/outputs/task_schedule_detail.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,193 +478,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>477.3</v>
+        <v>476.5</v>
       </c>
       <c r="D2" t="n">
-        <v>478.8</v>
+        <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>8.161421775123378</v>
+        <v>33.3194923765982</v>
       </c>
       <c r="F2" t="n">
-        <v>1.865053761592514</v>
+        <v>1.075758934389986</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03894584876119576</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>0.3687318542526718</v>
+      </c>
+      <c r="H2" t="n">
+        <v>344.2523269038021</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>477.3</v>
+        <v>477.4</v>
       </c>
       <c r="D3" t="n">
-        <v>478.8</v>
+        <v>477.9</v>
       </c>
       <c r="E3" t="n">
-        <v>18.51165536324877</v>
+        <v>17.75830290889152</v>
       </c>
       <c r="F3" t="n">
-        <v>1.865053761592514</v>
+        <v>1.424643731129063</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03894584876119576</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>0.4995125612622293</v>
+      </c>
+      <c r="H3" t="n">
+        <v>74.21143220135684</v>
+      </c>
       <c r="I3" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>477.3</v>
+        <v>481.7</v>
       </c>
       <c r="D4" t="n">
-        <v>478.8</v>
+        <v>482.2</v>
       </c>
       <c r="E4" t="n">
-        <v>23.95545290583382</v>
+        <v>18.5617177203687</v>
       </c>
       <c r="F4" t="n">
-        <v>1.865053761592514</v>
+        <v>1.399370230795788</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03894584876119576</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>0.5315600482271498</v>
+      </c>
+      <c r="H4" t="n">
+        <v>238.9384255996108</v>
+      </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>477.5</v>
+        <v>488.6</v>
       </c>
       <c r="D5" t="n">
-        <v>479</v>
+        <v>489.1</v>
       </c>
       <c r="E5" t="n">
-        <v>15.71915157067668</v>
+        <v>14.57061700891862</v>
       </c>
       <c r="F5" t="n">
-        <v>1.858594428028922</v>
+        <v>1.474192729110699</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9570591196432338</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>1.347108637956333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>69.44866854639935</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>477.5</v>
+        <v>494.6</v>
       </c>
       <c r="D6" t="n">
-        <v>479</v>
+        <v>495.1</v>
       </c>
       <c r="E6" t="n">
-        <v>7.463485666996357</v>
+        <v>32.50947724559238</v>
       </c>
       <c r="F6" t="n">
-        <v>1.858594428028922</v>
+        <v>1.477694687759484</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9570591196432338</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>0.8149988017620807</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.12420817847078</v>
+      </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>477.5</v>
+        <v>507.8</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>508.3</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54689737828631</v>
+        <v>28.06829128083212</v>
       </c>
       <c r="F7" t="n">
-        <v>1.858594428028922</v>
+        <v>0.698032640265114</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9570591196432338</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>0.3688104416859423</v>
+      </c>
+      <c r="H7" t="n">
+        <v>299.359238451112</v>
+      </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,19 +685,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>508.4</v>
+        <v>513.8</v>
       </c>
       <c r="D8" t="n">
-        <v>509.9</v>
+        <v>515.3</v>
       </c>
       <c r="E8" t="n">
-        <v>16.86413639470659</v>
+        <v>9.722144788015315</v>
       </c>
       <c r="F8" t="n">
-        <v>1.368627202665584</v>
+        <v>1.119176756904293</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3549381677681985</v>
+        <v>0.2239339707316807</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
@@ -695,7 +707,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,22 +716,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>508.7</v>
+        <v>750.3</v>
       </c>
       <c r="D9" t="n">
-        <v>509.2</v>
+        <v>750.8</v>
       </c>
       <c r="E9" t="n">
-        <v>33.11613377032513</v>
+        <v>22.47888960013016</v>
       </c>
       <c r="F9" t="n">
-        <v>1.413602857059988</v>
+        <v>1.378390598852753</v>
       </c>
       <c r="G9" t="n">
-        <v>1.160139368790909</v>
+        <v>0.1422501616249193</v>
       </c>
       <c r="H9" t="n">
-        <v>279.8709426975848</v>
+        <v>269.0680860307804</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -728,40 +740,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>模拟射击</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>508.7</v>
+        <v>751</v>
       </c>
       <c r="D10" t="n">
-        <v>509.2</v>
+        <v>752.5</v>
       </c>
       <c r="E10" t="n">
-        <v>28.98587359315943</v>
+        <v>13.65994494845707</v>
       </c>
       <c r="F10" t="n">
-        <v>1.413602857059988</v>
+        <v>1.907285386922786</v>
       </c>
       <c r="G10" t="n">
-        <v>1.160139368790909</v>
-      </c>
-      <c r="H10" t="n">
-        <v>299.5085276481853</v>
-      </c>
+        <v>0.2000410184869913</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -770,53 +780,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>509</v>
+        <v>762</v>
       </c>
       <c r="D11" t="n">
-        <v>510.5</v>
+        <v>763.5</v>
       </c>
       <c r="E11" t="n">
-        <v>9.456402839060875</v>
+        <v>29.73530197242527</v>
       </c>
       <c r="F11" t="n">
-        <v>1.035871434042922</v>
+        <v>0.9976030876011409</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9719349496075563</v>
+        <v>0.269833126546128</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>模拟射击</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>764.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>766.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>21.72832706699923</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.523432666310211</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.4568397284056099</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
         <v>0.85</v>
       </c>
     </row>
